--- a/iwpb-sg-dashboard/sample/IWPB_RealModel_Cols.xlsx
+++ b/iwpb-sg-dashboard/sample/IWPB_RealModel_Cols.xlsx
@@ -1311,31 +1311,31 @@
         <v>112.43</v>
       </c>
       <c r="AI3" t="n">
-        <v>224.85</v>
+        <v>226.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>337.28</v>
+        <v>339.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>449.71</v>
+        <v>452.41</v>
       </c>
       <c r="AL3" t="n">
-        <v>562.14</v>
+        <v>565.51</v>
       </c>
       <c r="AM3" t="n">
-        <v>674.5599999999999</v>
+        <v>678.61</v>
       </c>
       <c r="AN3" t="n">
-        <v>337.28</v>
+        <v>337.96</v>
       </c>
       <c r="AO3" t="n">
-        <v>337.28</v>
+        <v>337.96</v>
       </c>
       <c r="AP3" t="n">
-        <v>337.28</v>
+        <v>337.96</v>
       </c>
       <c r="AQ3" t="n">
-        <v>337.28</v>
+        <v>337.96</v>
       </c>
       <c r="AR3" t="n">
         <v>117.11</v>
@@ -1374,88 +1374,88 @@
         <v>120.62</v>
       </c>
       <c r="BD3" t="n">
-        <v>351.33</v>
+        <v>352.04</v>
       </c>
       <c r="BE3" t="n">
-        <v>351.33</v>
+        <v>352.04</v>
       </c>
       <c r="BF3" t="n">
-        <v>361.87</v>
+        <v>362.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>361.87</v>
+        <v>362.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>234.22</v>
+        <v>235.63</v>
       </c>
       <c r="BI3" t="n">
-        <v>351.33</v>
+        <v>353.44</v>
       </c>
       <c r="BJ3" t="n">
-        <v>468.45</v>
+        <v>471.26</v>
       </c>
       <c r="BK3" t="n">
-        <v>585.5599999999999</v>
+        <v>589.0700000000001</v>
       </c>
       <c r="BL3" t="n">
-        <v>702.67</v>
+        <v>706.89</v>
       </c>
       <c r="BM3" t="n">
         <v>120.62</v>
       </c>
       <c r="BN3" t="n">
-        <v>241.25</v>
+        <v>242.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>361.87</v>
+        <v>364.05</v>
       </c>
       <c r="BP3" t="n">
-        <v>482.5</v>
+        <v>485.39</v>
       </c>
       <c r="BQ3" t="n">
-        <v>603.12</v>
+        <v>606.74</v>
       </c>
       <c r="BR3" t="n">
-        <v>723.75</v>
+        <v>728.09</v>
       </c>
       <c r="BS3" t="n">
-        <v>1447.5</v>
+        <v>1453.29</v>
       </c>
       <c r="BT3" t="n">
-        <v>1349.12</v>
+        <v>1354.52</v>
       </c>
       <c r="BU3" t="n">
         <v>126.48</v>
       </c>
       <c r="BV3" t="n">
-        <v>1517.77</v>
+        <v>1523.84</v>
       </c>
       <c r="BW3" t="n">
-        <v>252.96</v>
+        <v>254.48</v>
       </c>
       <c r="BX3" t="n">
-        <v>379.44</v>
+        <v>381.72</v>
       </c>
       <c r="BY3" t="n">
-        <v>505.92</v>
+        <v>508.96</v>
       </c>
       <c r="BZ3" t="n">
-        <v>632.4</v>
+        <v>636.2</v>
       </c>
       <c r="CA3" t="n">
-        <v>758.88</v>
+        <v>763.4400000000001</v>
       </c>
       <c r="CB3" t="n">
-        <v>379.44</v>
+        <v>380.2</v>
       </c>
       <c r="CC3" t="n">
-        <v>379.44</v>
+        <v>380.2</v>
       </c>
       <c r="CD3" t="n">
-        <v>379.44</v>
+        <v>380.2</v>
       </c>
       <c r="CE3" t="n">
-        <v>379.44</v>
+        <v>380.2</v>
       </c>
     </row>
     <row r="4">
@@ -1606,31 +1606,31 @@
         <v>87.65000000000001</v>
       </c>
       <c r="AI4" t="n">
-        <v>175.3</v>
+        <v>176.35</v>
       </c>
       <c r="AJ4" t="n">
-        <v>262.95</v>
+        <v>264.53</v>
       </c>
       <c r="AK4" t="n">
-        <v>350.6</v>
+        <v>352.7</v>
       </c>
       <c r="AL4" t="n">
-        <v>438.25</v>
+        <v>440.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>525.9</v>
+        <v>529.05</v>
       </c>
       <c r="AN4" t="n">
-        <v>262.95</v>
+        <v>263.47</v>
       </c>
       <c r="AO4" t="n">
-        <v>262.95</v>
+        <v>263.47</v>
       </c>
       <c r="AP4" t="n">
-        <v>262.95</v>
+        <v>263.47</v>
       </c>
       <c r="AQ4" t="n">
-        <v>262.95</v>
+        <v>263.47</v>
       </c>
       <c r="AR4" t="n">
         <v>91.3</v>
@@ -1669,88 +1669,88 @@
         <v>94.04000000000001</v>
       </c>
       <c r="BD4" t="n">
-        <v>273.9</v>
+        <v>274.45</v>
       </c>
       <c r="BE4" t="n">
-        <v>273.9</v>
+        <v>274.45</v>
       </c>
       <c r="BF4" t="n">
-        <v>282.12</v>
+        <v>282.69</v>
       </c>
       <c r="BG4" t="n">
-        <v>282.12</v>
+        <v>282.69</v>
       </c>
       <c r="BH4" t="n">
-        <v>182.6</v>
+        <v>183.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>273.9</v>
+        <v>275.55</v>
       </c>
       <c r="BJ4" t="n">
-        <v>365.21</v>
+        <v>367.4</v>
       </c>
       <c r="BK4" t="n">
-        <v>456.51</v>
+        <v>459.25</v>
       </c>
       <c r="BL4" t="n">
-        <v>547.8099999999999</v>
+        <v>551.1</v>
       </c>
       <c r="BM4" t="n">
         <v>94.04000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>188.08</v>
+        <v>189.21</v>
       </c>
       <c r="BO4" t="n">
-        <v>282.12</v>
+        <v>283.81</v>
       </c>
       <c r="BP4" t="n">
-        <v>376.16</v>
+        <v>378.42</v>
       </c>
       <c r="BQ4" t="n">
-        <v>470.2</v>
+        <v>473.02</v>
       </c>
       <c r="BR4" t="n">
-        <v>564.24</v>
+        <v>567.63</v>
       </c>
       <c r="BS4" t="n">
-        <v>1128.49</v>
+        <v>1133</v>
       </c>
       <c r="BT4" t="n">
-        <v>1051.79</v>
+        <v>1056</v>
       </c>
       <c r="BU4" t="n">
         <v>98.61</v>
       </c>
       <c r="BV4" t="n">
-        <v>1183.27</v>
+        <v>1188</v>
       </c>
       <c r="BW4" t="n">
-        <v>197.21</v>
+        <v>198.39</v>
       </c>
       <c r="BX4" t="n">
-        <v>295.82</v>
+        <v>297.59</v>
       </c>
       <c r="BY4" t="n">
-        <v>394.42</v>
+        <v>396.79</v>
       </c>
       <c r="BZ4" t="n">
-        <v>493.03</v>
+        <v>495.99</v>
       </c>
       <c r="CA4" t="n">
-        <v>591.63</v>
+        <v>595.1799999999999</v>
       </c>
       <c r="CB4" t="n">
-        <v>295.82</v>
+        <v>296.41</v>
       </c>
       <c r="CC4" t="n">
-        <v>295.82</v>
+        <v>296.41</v>
       </c>
       <c r="CD4" t="n">
-        <v>295.82</v>
+        <v>296.41</v>
       </c>
       <c r="CE4" t="n">
-        <v>295.82</v>
+        <v>296.41</v>
       </c>
     </row>
     <row r="5">
@@ -1901,31 +1901,31 @@
         <v>201.77</v>
       </c>
       <c r="AI5" t="n">
-        <v>403.53</v>
+        <v>405.95</v>
       </c>
       <c r="AJ5" t="n">
-        <v>605.3</v>
+        <v>608.9299999999999</v>
       </c>
       <c r="AK5" t="n">
-        <v>807.0599999999999</v>
+        <v>811.91</v>
       </c>
       <c r="AL5" t="n">
-        <v>1008.83</v>
+        <v>1014.88</v>
       </c>
       <c r="AM5" t="n">
-        <v>1210.6</v>
+        <v>1217.86</v>
       </c>
       <c r="AN5" t="n">
-        <v>605.3</v>
+        <v>606.51</v>
       </c>
       <c r="AO5" t="n">
-        <v>605.3</v>
+        <v>606.51</v>
       </c>
       <c r="AP5" t="n">
-        <v>605.3</v>
+        <v>606.51</v>
       </c>
       <c r="AQ5" t="n">
-        <v>605.3</v>
+        <v>606.51</v>
       </c>
       <c r="AR5" t="n">
         <v>210.17</v>
@@ -1964,88 +1964,88 @@
         <v>216.48</v>
       </c>
       <c r="BD5" t="n">
-        <v>630.52</v>
+        <v>631.78</v>
       </c>
       <c r="BE5" t="n">
-        <v>630.52</v>
+        <v>631.78</v>
       </c>
       <c r="BF5" t="n">
-        <v>649.4299999999999</v>
+        <v>650.73</v>
       </c>
       <c r="BG5" t="n">
-        <v>649.4299999999999</v>
+        <v>650.73</v>
       </c>
       <c r="BH5" t="n">
-        <v>420.35</v>
+        <v>422.87</v>
       </c>
       <c r="BI5" t="n">
-        <v>630.52</v>
+        <v>634.3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>840.6900000000001</v>
+        <v>845.74</v>
       </c>
       <c r="BK5" t="n">
-        <v>1050.86</v>
+        <v>1057.17</v>
       </c>
       <c r="BL5" t="n">
-        <v>1261.04</v>
+        <v>1268.6</v>
       </c>
       <c r="BM5" t="n">
         <v>216.48</v>
       </c>
       <c r="BN5" t="n">
-        <v>432.96</v>
+        <v>435.55</v>
       </c>
       <c r="BO5" t="n">
-        <v>649.4299999999999</v>
+        <v>653.33</v>
       </c>
       <c r="BP5" t="n">
-        <v>865.91</v>
+        <v>871.11</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1082.39</v>
+        <v>1088.88</v>
       </c>
       <c r="BR5" t="n">
-        <v>1298.87</v>
+        <v>1306.66</v>
       </c>
       <c r="BS5" t="n">
-        <v>2597.74</v>
+        <v>2608.13</v>
       </c>
       <c r="BT5" t="n">
-        <v>2421.19</v>
+        <v>2430.88</v>
       </c>
       <c r="BU5" t="n">
         <v>226.99</v>
       </c>
       <c r="BV5" t="n">
-        <v>2723.84</v>
+        <v>2734.74</v>
       </c>
       <c r="BW5" t="n">
-        <v>453.97</v>
+        <v>456.7</v>
       </c>
       <c r="BX5" t="n">
-        <v>680.96</v>
+        <v>685.05</v>
       </c>
       <c r="BY5" t="n">
-        <v>907.95</v>
+        <v>913.39</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1134.93</v>
+        <v>1141.74</v>
       </c>
       <c r="CA5" t="n">
-        <v>1361.92</v>
+        <v>1370.09</v>
       </c>
       <c r="CB5" t="n">
-        <v>680.96</v>
+        <v>682.3200000000001</v>
       </c>
       <c r="CC5" t="n">
-        <v>680.96</v>
+        <v>682.3200000000001</v>
       </c>
       <c r="CD5" t="n">
-        <v>680.96</v>
+        <v>682.3200000000001</v>
       </c>
       <c r="CE5" t="n">
-        <v>680.96</v>
+        <v>682.3200000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2196,31 +2196,31 @@
         <v>-197.13</v>
       </c>
       <c r="AI6" t="n">
-        <v>-394.26</v>
+        <v>-396.63</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-591.39</v>
+        <v>-594.9400000000001</v>
       </c>
       <c r="AK6" t="n">
-        <v>-788.52</v>
+        <v>-793.25</v>
       </c>
       <c r="AL6" t="n">
-        <v>-985.65</v>
+        <v>-991.5599999999999</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1182.78</v>
+        <v>-1189.88</v>
       </c>
       <c r="AN6" t="n">
-        <v>-591.39</v>
+        <v>-592.5700000000001</v>
       </c>
       <c r="AO6" t="n">
-        <v>-591.39</v>
+        <v>-592.5700000000001</v>
       </c>
       <c r="AP6" t="n">
-        <v>-591.39</v>
+        <v>-592.5700000000001</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-591.39</v>
+        <v>-592.5700000000001</v>
       </c>
       <c r="AR6" t="n">
         <v>-205.34</v>
@@ -2259,88 +2259,88 @@
         <v>-211.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>-616.03</v>
+        <v>-617.26</v>
       </c>
       <c r="BE6" t="n">
-        <v>-616.03</v>
+        <v>-617.26</v>
       </c>
       <c r="BF6" t="n">
-        <v>-634.51</v>
+        <v>-635.78</v>
       </c>
       <c r="BG6" t="n">
-        <v>-634.51</v>
+        <v>-635.78</v>
       </c>
       <c r="BH6" t="n">
-        <v>-410.69</v>
+        <v>-413.15</v>
       </c>
       <c r="BI6" t="n">
-        <v>-616.03</v>
+        <v>-619.73</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-821.38</v>
+        <v>-826.3</v>
       </c>
       <c r="BK6" t="n">
-        <v>-1026.72</v>
+        <v>-1032.88</v>
       </c>
       <c r="BL6" t="n">
-        <v>-1232.06</v>
+        <v>-1239.46</v>
       </c>
       <c r="BM6" t="n">
         <v>-211.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>-423.01</v>
+        <v>-425.55</v>
       </c>
       <c r="BO6" t="n">
-        <v>-634.51</v>
+        <v>-638.3200000000001</v>
       </c>
       <c r="BP6" t="n">
-        <v>-846.02</v>
+        <v>-851.09</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-1057.52</v>
+        <v>-1063.87</v>
       </c>
       <c r="BR6" t="n">
-        <v>-1269.03</v>
+        <v>-1276.64</v>
       </c>
       <c r="BS6" t="n">
-        <v>-2538.05</v>
+        <v>-2548.2</v>
       </c>
       <c r="BT6" t="n">
-        <v>-2365.56</v>
+        <v>-2375.02</v>
       </c>
       <c r="BU6" t="n">
         <v>-221.77</v>
       </c>
       <c r="BV6" t="n">
-        <v>-2661.26</v>
+        <v>-2671.9</v>
       </c>
       <c r="BW6" t="n">
-        <v>-443.54</v>
+        <v>-446.2</v>
       </c>
       <c r="BX6" t="n">
-        <v>-665.3099999999999</v>
+        <v>-669.3099999999999</v>
       </c>
       <c r="BY6" t="n">
-        <v>-887.09</v>
+        <v>-892.41</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-1108.86</v>
+        <v>-1115.51</v>
       </c>
       <c r="CA6" t="n">
-        <v>-1330.63</v>
+        <v>-1338.61</v>
       </c>
       <c r="CB6" t="n">
-        <v>-665.3099999999999</v>
+        <v>-666.64</v>
       </c>
       <c r="CC6" t="n">
-        <v>-665.3099999999999</v>
+        <v>-666.64</v>
       </c>
       <c r="CD6" t="n">
-        <v>-665.3099999999999</v>
+        <v>-666.64</v>
       </c>
       <c r="CE6" t="n">
-        <v>-665.3099999999999</v>
+        <v>-666.64</v>
       </c>
     </row>
     <row r="7">
@@ -2491,31 +2491,31 @@
         <v>-117.36</v>
       </c>
       <c r="AI7" t="n">
-        <v>-234.71</v>
+        <v>-236.12</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-352.07</v>
+        <v>-354.18</v>
       </c>
       <c r="AK7" t="n">
-        <v>-469.42</v>
+        <v>-472.24</v>
       </c>
       <c r="AL7" t="n">
-        <v>-586.78</v>
+        <v>-590.3</v>
       </c>
       <c r="AM7" t="n">
-        <v>-704.13</v>
+        <v>-708.36</v>
       </c>
       <c r="AN7" t="n">
-        <v>-352.07</v>
+        <v>-352.77</v>
       </c>
       <c r="AO7" t="n">
-        <v>-352.07</v>
+        <v>-352.77</v>
       </c>
       <c r="AP7" t="n">
-        <v>-352.07</v>
+        <v>-352.77</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-352.07</v>
+        <v>-352.77</v>
       </c>
       <c r="AR7" t="n">
         <v>-122.24</v>
@@ -2554,88 +2554,88 @@
         <v>-125.91</v>
       </c>
       <c r="BD7" t="n">
-        <v>-366.73</v>
+        <v>-367.47</v>
       </c>
       <c r="BE7" t="n">
-        <v>-366.73</v>
+        <v>-367.47</v>
       </c>
       <c r="BF7" t="n">
-        <v>-377.74</v>
+        <v>-378.49</v>
       </c>
       <c r="BG7" t="n">
-        <v>-377.74</v>
+        <v>-378.49</v>
       </c>
       <c r="BH7" t="n">
-        <v>-244.49</v>
+        <v>-245.96</v>
       </c>
       <c r="BI7" t="n">
-        <v>-366.73</v>
+        <v>-368.94</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-488.98</v>
+        <v>-491.91</v>
       </c>
       <c r="BK7" t="n">
-        <v>-611.22</v>
+        <v>-614.89</v>
       </c>
       <c r="BL7" t="n">
-        <v>-733.47</v>
+        <v>-737.87</v>
       </c>
       <c r="BM7" t="n">
         <v>-125.91</v>
       </c>
       <c r="BN7" t="n">
-        <v>-251.82</v>
+        <v>-253.34</v>
       </c>
       <c r="BO7" t="n">
-        <v>-377.74</v>
+        <v>-380</v>
       </c>
       <c r="BP7" t="n">
-        <v>-503.65</v>
+        <v>-506.67</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-629.5599999999999</v>
+        <v>-633.34</v>
       </c>
       <c r="BR7" t="n">
-        <v>-755.47</v>
+        <v>-760.01</v>
       </c>
       <c r="BS7" t="n">
-        <v>-1510.95</v>
+        <v>-1516.99</v>
       </c>
       <c r="BT7" t="n">
-        <v>-1408.26</v>
+        <v>-1413.9</v>
       </c>
       <c r="BU7" t="n">
         <v>-132.02</v>
       </c>
       <c r="BV7" t="n">
-        <v>-1584.29</v>
+        <v>-1590.63</v>
       </c>
       <c r="BW7" t="n">
-        <v>-264.05</v>
+        <v>-265.63</v>
       </c>
       <c r="BX7" t="n">
-        <v>-396.07</v>
+        <v>-398.45</v>
       </c>
       <c r="BY7" t="n">
-        <v>-528.1</v>
+        <v>-531.27</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-660.12</v>
+        <v>-664.08</v>
       </c>
       <c r="CA7" t="n">
-        <v>-792.15</v>
+        <v>-796.9</v>
       </c>
       <c r="CB7" t="n">
-        <v>-396.07</v>
+        <v>-396.87</v>
       </c>
       <c r="CC7" t="n">
-        <v>-396.07</v>
+        <v>-396.87</v>
       </c>
       <c r="CD7" t="n">
-        <v>-396.07</v>
+        <v>-396.87</v>
       </c>
       <c r="CE7" t="n">
-        <v>-396.07</v>
+        <v>-396.87</v>
       </c>
     </row>
     <row r="8">
@@ -2786,31 +2786,31 @@
         <v>101.78</v>
       </c>
       <c r="AI8" t="n">
-        <v>203.56</v>
+        <v>204.78</v>
       </c>
       <c r="AJ8" t="n">
-        <v>305.33</v>
+        <v>307.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>407.11</v>
+        <v>409.55</v>
       </c>
       <c r="AL8" t="n">
-        <v>508.89</v>
+        <v>511.94</v>
       </c>
       <c r="AM8" t="n">
-        <v>610.67</v>
+        <v>614.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>305.33</v>
+        <v>305.94</v>
       </c>
       <c r="AO8" t="n">
-        <v>305.33</v>
+        <v>305.94</v>
       </c>
       <c r="AP8" t="n">
-        <v>305.33</v>
+        <v>305.94</v>
       </c>
       <c r="AQ8" t="n">
-        <v>305.33</v>
+        <v>305.94</v>
       </c>
       <c r="AR8" t="n">
         <v>106.02</v>
@@ -2849,88 +2849,88 @@
         <v>109.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>318.06</v>
+        <v>318.69</v>
       </c>
       <c r="BE8" t="n">
-        <v>318.06</v>
+        <v>318.69</v>
       </c>
       <c r="BF8" t="n">
-        <v>327.6</v>
+        <v>328.25</v>
       </c>
       <c r="BG8" t="n">
-        <v>327.6</v>
+        <v>328.25</v>
       </c>
       <c r="BH8" t="n">
-        <v>212.04</v>
+        <v>213.31</v>
       </c>
       <c r="BI8" t="n">
-        <v>318.06</v>
+        <v>319.96</v>
       </c>
       <c r="BJ8" t="n">
-        <v>424.07</v>
+        <v>426.62</v>
       </c>
       <c r="BK8" t="n">
-        <v>530.09</v>
+        <v>533.27</v>
       </c>
       <c r="BL8" t="n">
-        <v>636.11</v>
+        <v>639.9299999999999</v>
       </c>
       <c r="BM8" t="n">
         <v>109.2</v>
       </c>
       <c r="BN8" t="n">
-        <v>218.4</v>
+        <v>219.71</v>
       </c>
       <c r="BO8" t="n">
-        <v>327.6</v>
+        <v>329.56</v>
       </c>
       <c r="BP8" t="n">
-        <v>436.8</v>
+        <v>439.42</v>
       </c>
       <c r="BQ8" t="n">
-        <v>546</v>
+        <v>549.27</v>
       </c>
       <c r="BR8" t="n">
-        <v>655.1900000000001</v>
+        <v>659.13</v>
       </c>
       <c r="BS8" t="n">
-        <v>1310.39</v>
+        <v>1315.63</v>
       </c>
       <c r="BT8" t="n">
-        <v>1221.33</v>
+        <v>1226.22</v>
       </c>
       <c r="BU8" t="n">
         <v>114.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>1374</v>
+        <v>1379.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>229</v>
+        <v>230.37</v>
       </c>
       <c r="BX8" t="n">
-        <v>343.5</v>
+        <v>345.56</v>
       </c>
       <c r="BY8" t="n">
-        <v>458</v>
+        <v>460.75</v>
       </c>
       <c r="BZ8" t="n">
-        <v>572.5</v>
+        <v>575.9400000000001</v>
       </c>
       <c r="CA8" t="n">
-        <v>687</v>
+        <v>691.12</v>
       </c>
       <c r="CB8" t="n">
-        <v>343.5</v>
+        <v>344.19</v>
       </c>
       <c r="CC8" t="n">
-        <v>343.5</v>
+        <v>344.19</v>
       </c>
       <c r="CD8" t="n">
-        <v>343.5</v>
+        <v>344.19</v>
       </c>
       <c r="CE8" t="n">
-        <v>343.5</v>
+        <v>344.19</v>
       </c>
     </row>
     <row r="9">
@@ -3081,31 +3081,31 @@
         <v>182.24</v>
       </c>
       <c r="AI9" t="n">
-        <v>364.48</v>
+        <v>366.67</v>
       </c>
       <c r="AJ9" t="n">
-        <v>546.72</v>
+        <v>550</v>
       </c>
       <c r="AK9" t="n">
-        <v>728.96</v>
+        <v>733.34</v>
       </c>
       <c r="AL9" t="n">
-        <v>911.2</v>
+        <v>916.67</v>
       </c>
       <c r="AM9" t="n">
-        <v>1093.44</v>
+        <v>1100</v>
       </c>
       <c r="AN9" t="n">
-        <v>546.72</v>
+        <v>547.8099999999999</v>
       </c>
       <c r="AO9" t="n">
-        <v>546.72</v>
+        <v>547.8099999999999</v>
       </c>
       <c r="AP9" t="n">
-        <v>546.72</v>
+        <v>547.8099999999999</v>
       </c>
       <c r="AQ9" t="n">
-        <v>546.72</v>
+        <v>547.8099999999999</v>
       </c>
       <c r="AR9" t="n">
         <v>189.83</v>
@@ -3144,88 +3144,88 @@
         <v>195.53</v>
       </c>
       <c r="BD9" t="n">
-        <v>569.5</v>
+        <v>570.64</v>
       </c>
       <c r="BE9" t="n">
-        <v>569.5</v>
+        <v>570.64</v>
       </c>
       <c r="BF9" t="n">
-        <v>586.59</v>
+        <v>587.76</v>
       </c>
       <c r="BG9" t="n">
-        <v>586.59</v>
+        <v>587.76</v>
       </c>
       <c r="BH9" t="n">
-        <v>379.67</v>
+        <v>381.95</v>
       </c>
       <c r="BI9" t="n">
-        <v>569.5</v>
+        <v>572.92</v>
       </c>
       <c r="BJ9" t="n">
-        <v>759.33</v>
+        <v>763.89</v>
       </c>
       <c r="BK9" t="n">
-        <v>949.17</v>
+        <v>954.86</v>
       </c>
       <c r="BL9" t="n">
-        <v>1139</v>
+        <v>1145.84</v>
       </c>
       <c r="BM9" t="n">
         <v>195.53</v>
       </c>
       <c r="BN9" t="n">
-        <v>391.06</v>
+        <v>393.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>586.59</v>
+        <v>590.11</v>
       </c>
       <c r="BP9" t="n">
-        <v>782.11</v>
+        <v>786.8099999999999</v>
       </c>
       <c r="BQ9" t="n">
-        <v>977.64</v>
+        <v>983.51</v>
       </c>
       <c r="BR9" t="n">
-        <v>1173.17</v>
+        <v>1180.21</v>
       </c>
       <c r="BS9" t="n">
-        <v>2346.34</v>
+        <v>2355.73</v>
       </c>
       <c r="BT9" t="n">
-        <v>2186.88</v>
+        <v>2195.63</v>
       </c>
       <c r="BU9" t="n">
         <v>205.02</v>
       </c>
       <c r="BV9" t="n">
-        <v>2460.25</v>
+        <v>2470.09</v>
       </c>
       <c r="BW9" t="n">
-        <v>410.04</v>
+        <v>412.5</v>
       </c>
       <c r="BX9" t="n">
-        <v>615.0599999999999</v>
+        <v>618.75</v>
       </c>
       <c r="BY9" t="n">
-        <v>820.08</v>
+        <v>825</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1025.1</v>
+        <v>1031.25</v>
       </c>
       <c r="CA9" t="n">
-        <v>1230.12</v>
+        <v>1237.5</v>
       </c>
       <c r="CB9" t="n">
-        <v>615.0599999999999</v>
+        <v>616.29</v>
       </c>
       <c r="CC9" t="n">
-        <v>615.0599999999999</v>
+        <v>616.29</v>
       </c>
       <c r="CD9" t="n">
-        <v>615.0599999999999</v>
+        <v>616.29</v>
       </c>
       <c r="CE9" t="n">
-        <v>615.0599999999999</v>
+        <v>616.29</v>
       </c>
     </row>
     <row r="10">
@@ -3376,31 +3376,31 @@
         <v>167.35</v>
       </c>
       <c r="AI10" t="n">
-        <v>334.7</v>
+        <v>336.71</v>
       </c>
       <c r="AJ10" t="n">
-        <v>502.06</v>
+        <v>505.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>669.41</v>
+        <v>673.42</v>
       </c>
       <c r="AL10" t="n">
-        <v>836.76</v>
+        <v>841.78</v>
       </c>
       <c r="AM10" t="n">
-        <v>1004.11</v>
+        <v>1010.14</v>
       </c>
       <c r="AN10" t="n">
-        <v>502.06</v>
+        <v>503.06</v>
       </c>
       <c r="AO10" t="n">
-        <v>502.06</v>
+        <v>503.06</v>
       </c>
       <c r="AP10" t="n">
-        <v>502.06</v>
+        <v>503.06</v>
       </c>
       <c r="AQ10" t="n">
-        <v>502.06</v>
+        <v>503.06</v>
       </c>
       <c r="AR10" t="n">
         <v>174.32</v>
@@ -3439,88 +3439,88 @@
         <v>179.55</v>
       </c>
       <c r="BD10" t="n">
-        <v>522.97</v>
+        <v>524.02</v>
       </c>
       <c r="BE10" t="n">
-        <v>522.97</v>
+        <v>524.02</v>
       </c>
       <c r="BF10" t="n">
-        <v>538.66</v>
+        <v>539.74</v>
       </c>
       <c r="BG10" t="n">
-        <v>538.66</v>
+        <v>539.74</v>
       </c>
       <c r="BH10" t="n">
-        <v>348.65</v>
+        <v>350.74</v>
       </c>
       <c r="BI10" t="n">
-        <v>522.97</v>
+        <v>526.11</v>
       </c>
       <c r="BJ10" t="n">
-        <v>697.3</v>
+        <v>701.48</v>
       </c>
       <c r="BK10" t="n">
-        <v>871.62</v>
+        <v>876.85</v>
       </c>
       <c r="BL10" t="n">
-        <v>1045.95</v>
+        <v>1052.22</v>
       </c>
       <c r="BM10" t="n">
         <v>179.55</v>
       </c>
       <c r="BN10" t="n">
-        <v>359.11</v>
+        <v>361.26</v>
       </c>
       <c r="BO10" t="n">
-        <v>538.66</v>
+        <v>541.9</v>
       </c>
       <c r="BP10" t="n">
-        <v>718.22</v>
+        <v>722.53</v>
       </c>
       <c r="BQ10" t="n">
-        <v>897.77</v>
+        <v>903.16</v>
       </c>
       <c r="BR10" t="n">
-        <v>1077.33</v>
+        <v>1083.79</v>
       </c>
       <c r="BS10" t="n">
-        <v>2154.65</v>
+        <v>2163.27</v>
       </c>
       <c r="BT10" t="n">
-        <v>2008.22</v>
+        <v>2016.25</v>
       </c>
       <c r="BU10" t="n">
         <v>188.27</v>
       </c>
       <c r="BV10" t="n">
-        <v>2259.25</v>
+        <v>2268.29</v>
       </c>
       <c r="BW10" t="n">
-        <v>376.54</v>
+        <v>378.8</v>
       </c>
       <c r="BX10" t="n">
-        <v>564.8099999999999</v>
+        <v>568.2</v>
       </c>
       <c r="BY10" t="n">
-        <v>753.08</v>
+        <v>757.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>941.35</v>
+        <v>947</v>
       </c>
       <c r="CA10" t="n">
-        <v>1129.62</v>
+        <v>1136.4</v>
       </c>
       <c r="CB10" t="n">
-        <v>564.8099999999999</v>
+        <v>565.9400000000001</v>
       </c>
       <c r="CC10" t="n">
-        <v>564.8099999999999</v>
+        <v>565.9400000000001</v>
       </c>
       <c r="CD10" t="n">
-        <v>564.8099999999999</v>
+        <v>565.9400000000001</v>
       </c>
       <c r="CE10" t="n">
-        <v>564.8099999999999</v>
+        <v>565.9400000000001</v>
       </c>
     </row>
     <row r="11">
@@ -3671,31 +3671,31 @@
         <v>-111.03</v>
       </c>
       <c r="AI11" t="n">
-        <v>-222.07</v>
+        <v>-223.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-333.1</v>
+        <v>-335.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>-444.14</v>
+        <v>-446.8</v>
       </c>
       <c r="AL11" t="n">
-        <v>-555.17</v>
+        <v>-558.51</v>
       </c>
       <c r="AM11" t="n">
-        <v>-666.21</v>
+        <v>-670.21</v>
       </c>
       <c r="AN11" t="n">
-        <v>-333.1</v>
+        <v>-333.77</v>
       </c>
       <c r="AO11" t="n">
-        <v>-333.1</v>
+        <v>-333.77</v>
       </c>
       <c r="AP11" t="n">
-        <v>-333.1</v>
+        <v>-333.77</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-333.1</v>
+        <v>-333.77</v>
       </c>
       <c r="AR11" t="n">
         <v>-115.66</v>
@@ -3734,88 +3734,88 @@
         <v>-119.13</v>
       </c>
       <c r="BD11" t="n">
-        <v>-346.98</v>
+        <v>-347.68</v>
       </c>
       <c r="BE11" t="n">
-        <v>-346.98</v>
+        <v>-347.68</v>
       </c>
       <c r="BF11" t="n">
-        <v>-357.39</v>
+        <v>-358.11</v>
       </c>
       <c r="BG11" t="n">
-        <v>-357.39</v>
+        <v>-358.11</v>
       </c>
       <c r="BH11" t="n">
-        <v>-231.32</v>
+        <v>-232.71</v>
       </c>
       <c r="BI11" t="n">
-        <v>-346.98</v>
+        <v>-349.07</v>
       </c>
       <c r="BJ11" t="n">
-        <v>-462.65</v>
+        <v>-465.42</v>
       </c>
       <c r="BK11" t="n">
-        <v>-578.3099999999999</v>
+        <v>-581.78</v>
       </c>
       <c r="BL11" t="n">
-        <v>-693.97</v>
+        <v>-698.13</v>
       </c>
       <c r="BM11" t="n">
         <v>-119.13</v>
       </c>
       <c r="BN11" t="n">
-        <v>-238.26</v>
+        <v>-239.69</v>
       </c>
       <c r="BO11" t="n">
-        <v>-357.39</v>
+        <v>-359.54</v>
       </c>
       <c r="BP11" t="n">
-        <v>-476.52</v>
+        <v>-479.38</v>
       </c>
       <c r="BQ11" t="n">
-        <v>-595.66</v>
+        <v>-599.23</v>
       </c>
       <c r="BR11" t="n">
-        <v>-714.79</v>
+        <v>-719.08</v>
       </c>
       <c r="BS11" t="n">
-        <v>-1429.57</v>
+        <v>-1435.29</v>
       </c>
       <c r="BT11" t="n">
-        <v>-1332.42</v>
+        <v>-1337.75</v>
       </c>
       <c r="BU11" t="n">
         <v>-124.91</v>
       </c>
       <c r="BV11" t="n">
-        <v>-1498.97</v>
+        <v>-1504.97</v>
       </c>
       <c r="BW11" t="n">
-        <v>-249.83</v>
+        <v>-251.33</v>
       </c>
       <c r="BX11" t="n">
-        <v>-374.74</v>
+        <v>-376.99</v>
       </c>
       <c r="BY11" t="n">
-        <v>-499.66</v>
+        <v>-502.65</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-624.5700000000001</v>
+        <v>-628.3200000000001</v>
       </c>
       <c r="CA11" t="n">
-        <v>-749.49</v>
+        <v>-753.98</v>
       </c>
       <c r="CB11" t="n">
-        <v>-374.74</v>
+        <v>-375.49</v>
       </c>
       <c r="CC11" t="n">
-        <v>-374.74</v>
+        <v>-375.49</v>
       </c>
       <c r="CD11" t="n">
-        <v>-374.74</v>
+        <v>-375.49</v>
       </c>
       <c r="CE11" t="n">
-        <v>-374.74</v>
+        <v>-375.49</v>
       </c>
     </row>
     <row r="12">
@@ -3966,31 +3966,31 @@
         <v>-257.6</v>
       </c>
       <c r="AI12" t="n">
-        <v>-515.2</v>
+        <v>-518.29</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-772.79</v>
+        <v>-777.4299999999999</v>
       </c>
       <c r="AK12" t="n">
-        <v>-1030.39</v>
+        <v>-1036.57</v>
       </c>
       <c r="AL12" t="n">
-        <v>-1287.99</v>
+        <v>-1295.72</v>
       </c>
       <c r="AM12" t="n">
-        <v>-1545.59</v>
+        <v>-1554.86</v>
       </c>
       <c r="AN12" t="n">
-        <v>-772.79</v>
+        <v>-774.34</v>
       </c>
       <c r="AO12" t="n">
-        <v>-772.79</v>
+        <v>-774.34</v>
       </c>
       <c r="AP12" t="n">
-        <v>-772.79</v>
+        <v>-774.34</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-772.79</v>
+        <v>-774.34</v>
       </c>
       <c r="AR12" t="n">
         <v>-268.33</v>
@@ -4029,88 +4029,88 @@
         <v>-276.38</v>
       </c>
       <c r="BD12" t="n">
-        <v>-804.99</v>
+        <v>-806.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>-804.99</v>
+        <v>-806.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>-829.14</v>
+        <v>-830.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>-829.14</v>
+        <v>-830.8</v>
       </c>
       <c r="BH12" t="n">
-        <v>-536.66</v>
+        <v>-539.88</v>
       </c>
       <c r="BI12" t="n">
-        <v>-804.99</v>
+        <v>-809.8200000000001</v>
       </c>
       <c r="BJ12" t="n">
-        <v>-1073.32</v>
+        <v>-1079.76</v>
       </c>
       <c r="BK12" t="n">
-        <v>-1341.65</v>
+        <v>-1349.7</v>
       </c>
       <c r="BL12" t="n">
-        <v>-1609.99</v>
+        <v>-1619.65</v>
       </c>
       <c r="BM12" t="n">
         <v>-276.38</v>
       </c>
       <c r="BN12" t="n">
-        <v>-552.76</v>
+        <v>-556.08</v>
       </c>
       <c r="BO12" t="n">
-        <v>-829.14</v>
+        <v>-834.12</v>
       </c>
       <c r="BP12" t="n">
-        <v>-1105.52</v>
+        <v>-1112.16</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-1381.9</v>
+        <v>-1390.2</v>
       </c>
       <c r="BR12" t="n">
-        <v>-1658.28</v>
+        <v>-1668.23</v>
       </c>
       <c r="BS12" t="n">
-        <v>-3316.57</v>
+        <v>-3329.84</v>
       </c>
       <c r="BT12" t="n">
-        <v>-3091.17</v>
+        <v>-3103.54</v>
       </c>
       <c r="BU12" t="n">
         <v>-289.8</v>
       </c>
       <c r="BV12" t="n">
-        <v>-3477.57</v>
+        <v>-3491.48</v>
       </c>
       <c r="BW12" t="n">
-        <v>-579.59</v>
+        <v>-583.0700000000001</v>
       </c>
       <c r="BX12" t="n">
-        <v>-869.39</v>
+        <v>-874.61</v>
       </c>
       <c r="BY12" t="n">
-        <v>-1159.19</v>
+        <v>-1166.14</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-1448.99</v>
+        <v>-1457.68</v>
       </c>
       <c r="CA12" t="n">
-        <v>-1738.78</v>
+        <v>-1749.22</v>
       </c>
       <c r="CB12" t="n">
-        <v>-869.39</v>
+        <v>-871.13</v>
       </c>
       <c r="CC12" t="n">
-        <v>-869.39</v>
+        <v>-871.13</v>
       </c>
       <c r="CD12" t="n">
-        <v>-869.39</v>
+        <v>-871.13</v>
       </c>
       <c r="CE12" t="n">
-        <v>-869.39</v>
+        <v>-871.13</v>
       </c>
     </row>
   </sheetData>
@@ -5021,31 +5021,31 @@
         <v>147.44</v>
       </c>
       <c r="AI3" t="n">
-        <v>294.88</v>
+        <v>296.65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>442.32</v>
+        <v>444.98</v>
       </c>
       <c r="AK3" t="n">
-        <v>589.77</v>
+        <v>593.3</v>
       </c>
       <c r="AL3" t="n">
-        <v>737.21</v>
+        <v>741.63</v>
       </c>
       <c r="AM3" t="n">
-        <v>884.65</v>
+        <v>889.96</v>
       </c>
       <c r="AN3" t="n">
-        <v>442.32</v>
+        <v>443.21</v>
       </c>
       <c r="AO3" t="n">
-        <v>442.32</v>
+        <v>443.21</v>
       </c>
       <c r="AP3" t="n">
-        <v>442.32</v>
+        <v>443.21</v>
       </c>
       <c r="AQ3" t="n">
-        <v>442.32</v>
+        <v>443.21</v>
       </c>
       <c r="AR3" t="n">
         <v>153.58</v>
@@ -5084,88 +5084,88 @@
         <v>158.19</v>
       </c>
       <c r="BD3" t="n">
-        <v>460.75</v>
+        <v>461.68</v>
       </c>
       <c r="BE3" t="n">
-        <v>460.75</v>
+        <v>461.68</v>
       </c>
       <c r="BF3" t="n">
-        <v>474.58</v>
+        <v>475.53</v>
       </c>
       <c r="BG3" t="n">
-        <v>474.58</v>
+        <v>475.53</v>
       </c>
       <c r="BH3" t="n">
-        <v>307.17</v>
+        <v>309.01</v>
       </c>
       <c r="BI3" t="n">
-        <v>460.75</v>
+        <v>463.52</v>
       </c>
       <c r="BJ3" t="n">
-        <v>614.34</v>
+        <v>618.03</v>
       </c>
       <c r="BK3" t="n">
-        <v>767.92</v>
+        <v>772.53</v>
       </c>
       <c r="BL3" t="n">
-        <v>921.51</v>
+        <v>927.04</v>
       </c>
       <c r="BM3" t="n">
         <v>158.19</v>
       </c>
       <c r="BN3" t="n">
-        <v>316.38</v>
+        <v>318.28</v>
       </c>
       <c r="BO3" t="n">
-        <v>474.58</v>
+        <v>477.42</v>
       </c>
       <c r="BP3" t="n">
-        <v>632.77</v>
+        <v>636.5700000000001</v>
       </c>
       <c r="BQ3" t="n">
-        <v>790.96</v>
+        <v>795.71</v>
       </c>
       <c r="BR3" t="n">
-        <v>949.15</v>
+        <v>954.85</v>
       </c>
       <c r="BS3" t="n">
-        <v>1898.31</v>
+        <v>1905.9</v>
       </c>
       <c r="BT3" t="n">
-        <v>1769.3</v>
+        <v>1776.37</v>
       </c>
       <c r="BU3" t="n">
         <v>165.87</v>
       </c>
       <c r="BV3" t="n">
-        <v>1990.46</v>
+        <v>1998.42</v>
       </c>
       <c r="BW3" t="n">
-        <v>331.74</v>
+        <v>333.73</v>
       </c>
       <c r="BX3" t="n">
-        <v>497.61</v>
+        <v>500.6</v>
       </c>
       <c r="BY3" t="n">
-        <v>663.49</v>
+        <v>667.47</v>
       </c>
       <c r="BZ3" t="n">
-        <v>829.36</v>
+        <v>834.33</v>
       </c>
       <c r="CA3" t="n">
-        <v>995.23</v>
+        <v>1001.2</v>
       </c>
       <c r="CB3" t="n">
-        <v>497.61</v>
+        <v>498.61</v>
       </c>
       <c r="CC3" t="n">
-        <v>497.61</v>
+        <v>498.61</v>
       </c>
       <c r="CD3" t="n">
-        <v>497.61</v>
+        <v>498.61</v>
       </c>
       <c r="CE3" t="n">
-        <v>497.61</v>
+        <v>498.61</v>
       </c>
     </row>
     <row r="4">
@@ -5316,31 +5316,31 @@
         <v>212.29</v>
       </c>
       <c r="AI4" t="n">
-        <v>424.59</v>
+        <v>427.13</v>
       </c>
       <c r="AJ4" t="n">
-        <v>636.88</v>
+        <v>640.7</v>
       </c>
       <c r="AK4" t="n">
-        <v>849.17</v>
+        <v>854.27</v>
       </c>
       <c r="AL4" t="n">
-        <v>1061.47</v>
+        <v>1067.83</v>
       </c>
       <c r="AM4" t="n">
-        <v>1273.76</v>
+        <v>1281.4</v>
       </c>
       <c r="AN4" t="n">
-        <v>636.88</v>
+        <v>638.15</v>
       </c>
       <c r="AO4" t="n">
-        <v>636.88</v>
+        <v>638.15</v>
       </c>
       <c r="AP4" t="n">
-        <v>636.88</v>
+        <v>638.15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>636.88</v>
+        <v>638.15</v>
       </c>
       <c r="AR4" t="n">
         <v>221.14</v>
@@ -5379,88 +5379,88 @@
         <v>227.77</v>
       </c>
       <c r="BD4" t="n">
-        <v>663.42</v>
+        <v>664.74</v>
       </c>
       <c r="BE4" t="n">
-        <v>663.42</v>
+        <v>664.74</v>
       </c>
       <c r="BF4" t="n">
-        <v>683.3200000000001</v>
+        <v>684.6900000000001</v>
       </c>
       <c r="BG4" t="n">
-        <v>683.3200000000001</v>
+        <v>684.6900000000001</v>
       </c>
       <c r="BH4" t="n">
-        <v>442.28</v>
+        <v>444.93</v>
       </c>
       <c r="BI4" t="n">
-        <v>663.42</v>
+        <v>667.4</v>
       </c>
       <c r="BJ4" t="n">
-        <v>884.5599999999999</v>
+        <v>889.86</v>
       </c>
       <c r="BK4" t="n">
-        <v>1105.69</v>
+        <v>1112.33</v>
       </c>
       <c r="BL4" t="n">
-        <v>1326.83</v>
+        <v>1334.79</v>
       </c>
       <c r="BM4" t="n">
         <v>227.77</v>
       </c>
       <c r="BN4" t="n">
-        <v>455.55</v>
+        <v>458.28</v>
       </c>
       <c r="BO4" t="n">
-        <v>683.3200000000001</v>
+        <v>687.42</v>
       </c>
       <c r="BP4" t="n">
-        <v>911.09</v>
+        <v>916.5599999999999</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1138.86</v>
+        <v>1145.7</v>
       </c>
       <c r="BR4" t="n">
-        <v>1366.64</v>
+        <v>1374.84</v>
       </c>
       <c r="BS4" t="n">
-        <v>2733.28</v>
+        <v>2744.21</v>
       </c>
       <c r="BT4" t="n">
-        <v>2547.52</v>
+        <v>2557.71</v>
       </c>
       <c r="BU4" t="n">
         <v>238.83</v>
       </c>
       <c r="BV4" t="n">
-        <v>2865.96</v>
+        <v>2877.42</v>
       </c>
       <c r="BW4" t="n">
-        <v>477.66</v>
+        <v>480.53</v>
       </c>
       <c r="BX4" t="n">
-        <v>716.49</v>
+        <v>720.79</v>
       </c>
       <c r="BY4" t="n">
-        <v>955.3200000000001</v>
+        <v>961.05</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1194.15</v>
+        <v>1201.31</v>
       </c>
       <c r="CA4" t="n">
-        <v>1432.98</v>
+        <v>1441.58</v>
       </c>
       <c r="CB4" t="n">
-        <v>716.49</v>
+        <v>717.92</v>
       </c>
       <c r="CC4" t="n">
-        <v>716.49</v>
+        <v>717.92</v>
       </c>
       <c r="CD4" t="n">
-        <v>716.49</v>
+        <v>717.92</v>
       </c>
       <c r="CE4" t="n">
-        <v>716.49</v>
+        <v>717.92</v>
       </c>
     </row>
     <row r="5">
@@ -5611,31 +5611,31 @@
         <v>94.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>188.65</v>
+        <v>189.78</v>
       </c>
       <c r="AJ5" t="n">
-        <v>282.98</v>
+        <v>284.68</v>
       </c>
       <c r="AK5" t="n">
-        <v>377.3</v>
+        <v>379.57</v>
       </c>
       <c r="AL5" t="n">
-        <v>471.63</v>
+        <v>474.46</v>
       </c>
       <c r="AM5" t="n">
-        <v>565.95</v>
+        <v>569.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>282.98</v>
+        <v>283.54</v>
       </c>
       <c r="AO5" t="n">
-        <v>282.98</v>
+        <v>283.54</v>
       </c>
       <c r="AP5" t="n">
-        <v>282.98</v>
+        <v>283.54</v>
       </c>
       <c r="AQ5" t="n">
-        <v>282.98</v>
+        <v>283.54</v>
       </c>
       <c r="AR5" t="n">
         <v>98.26000000000001</v>
@@ -5674,88 +5674,88 @@
         <v>101.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>294.77</v>
+        <v>295.36</v>
       </c>
       <c r="BE5" t="n">
-        <v>294.77</v>
+        <v>295.36</v>
       </c>
       <c r="BF5" t="n">
-        <v>303.61</v>
+        <v>304.22</v>
       </c>
       <c r="BG5" t="n">
-        <v>303.61</v>
+        <v>304.22</v>
       </c>
       <c r="BH5" t="n">
-        <v>196.51</v>
+        <v>197.69</v>
       </c>
       <c r="BI5" t="n">
-        <v>294.77</v>
+        <v>296.54</v>
       </c>
       <c r="BJ5" t="n">
-        <v>393.02</v>
+        <v>395.38</v>
       </c>
       <c r="BK5" t="n">
-        <v>491.28</v>
+        <v>494.23</v>
       </c>
       <c r="BL5" t="n">
-        <v>589.54</v>
+        <v>593.0700000000001</v>
       </c>
       <c r="BM5" t="n">
         <v>101.2</v>
       </c>
       <c r="BN5" t="n">
-        <v>202.41</v>
+        <v>203.62</v>
       </c>
       <c r="BO5" t="n">
-        <v>303.61</v>
+        <v>305.43</v>
       </c>
       <c r="BP5" t="n">
-        <v>404.81</v>
+        <v>407.24</v>
       </c>
       <c r="BQ5" t="n">
-        <v>506.02</v>
+        <v>509.05</v>
       </c>
       <c r="BR5" t="n">
-        <v>607.22</v>
+        <v>610.87</v>
       </c>
       <c r="BS5" t="n">
-        <v>1214.44</v>
+        <v>1219.3</v>
       </c>
       <c r="BT5" t="n">
-        <v>1131.91</v>
+        <v>1136.44</v>
       </c>
       <c r="BU5" t="n">
         <v>106.12</v>
       </c>
       <c r="BV5" t="n">
-        <v>1273.4</v>
+        <v>1278.49</v>
       </c>
       <c r="BW5" t="n">
-        <v>212.23</v>
+        <v>213.51</v>
       </c>
       <c r="BX5" t="n">
-        <v>318.35</v>
+        <v>320.26</v>
       </c>
       <c r="BY5" t="n">
-        <v>424.47</v>
+        <v>427.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>530.58</v>
+        <v>533.77</v>
       </c>
       <c r="CA5" t="n">
-        <v>636.7</v>
+        <v>640.52</v>
       </c>
       <c r="CB5" t="n">
-        <v>318.35</v>
+        <v>318.99</v>
       </c>
       <c r="CC5" t="n">
-        <v>318.35</v>
+        <v>318.99</v>
       </c>
       <c r="CD5" t="n">
-        <v>318.35</v>
+        <v>318.99</v>
       </c>
       <c r="CE5" t="n">
-        <v>318.35</v>
+        <v>318.99</v>
       </c>
     </row>
     <row r="6">
@@ -5906,31 +5906,31 @@
         <v>-67.45999999999999</v>
       </c>
       <c r="AI6" t="n">
-        <v>-134.92</v>
+        <v>-135.73</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-202.38</v>
+        <v>-203.59</v>
       </c>
       <c r="AK6" t="n">
-        <v>-269.83</v>
+        <v>-271.45</v>
       </c>
       <c r="AL6" t="n">
-        <v>-337.29</v>
+        <v>-339.32</v>
       </c>
       <c r="AM6" t="n">
-        <v>-404.75</v>
+        <v>-407.18</v>
       </c>
       <c r="AN6" t="n">
-        <v>-202.38</v>
+        <v>-202.78</v>
       </c>
       <c r="AO6" t="n">
-        <v>-202.38</v>
+        <v>-202.78</v>
       </c>
       <c r="AP6" t="n">
-        <v>-202.38</v>
+        <v>-202.78</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-202.38</v>
+        <v>-202.78</v>
       </c>
       <c r="AR6" t="n">
         <v>-70.27</v>
@@ -5969,88 +5969,88 @@
         <v>-72.38</v>
       </c>
       <c r="BD6" t="n">
-        <v>-210.81</v>
+        <v>-211.23</v>
       </c>
       <c r="BE6" t="n">
-        <v>-210.81</v>
+        <v>-211.23</v>
       </c>
       <c r="BF6" t="n">
-        <v>-217.13</v>
+        <v>-217.57</v>
       </c>
       <c r="BG6" t="n">
-        <v>-217.13</v>
+        <v>-217.57</v>
       </c>
       <c r="BH6" t="n">
-        <v>-140.54</v>
+        <v>-141.38</v>
       </c>
       <c r="BI6" t="n">
-        <v>-210.81</v>
+        <v>-212.07</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-281.08</v>
+        <v>-282.76</v>
       </c>
       <c r="BK6" t="n">
-        <v>-351.35</v>
+        <v>-353.45</v>
       </c>
       <c r="BL6" t="n">
-        <v>-421.62</v>
+        <v>-424.15</v>
       </c>
       <c r="BM6" t="n">
         <v>-72.38</v>
       </c>
       <c r="BN6" t="n">
-        <v>-144.75</v>
+        <v>-145.62</v>
       </c>
       <c r="BO6" t="n">
-        <v>-217.13</v>
+        <v>-218.44</v>
       </c>
       <c r="BP6" t="n">
-        <v>-289.51</v>
+        <v>-291.25</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-361.89</v>
+        <v>-364.06</v>
       </c>
       <c r="BR6" t="n">
-        <v>-434.26</v>
+        <v>-436.87</v>
       </c>
       <c r="BS6" t="n">
-        <v>-868.53</v>
+        <v>-872</v>
       </c>
       <c r="BT6" t="n">
-        <v>-809.5</v>
+        <v>-812.74</v>
       </c>
       <c r="BU6" t="n">
         <v>-75.89</v>
       </c>
       <c r="BV6" t="n">
-        <v>-910.6900000000001</v>
+        <v>-914.33</v>
       </c>
       <c r="BW6" t="n">
-        <v>-151.78</v>
+        <v>-152.69</v>
       </c>
       <c r="BX6" t="n">
-        <v>-227.67</v>
+        <v>-229.04</v>
       </c>
       <c r="BY6" t="n">
-        <v>-303.56</v>
+        <v>-305.39</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-379.45</v>
+        <v>-381.73</v>
       </c>
       <c r="CA6" t="n">
-        <v>-455.35</v>
+        <v>-458.08</v>
       </c>
       <c r="CB6" t="n">
-        <v>-227.67</v>
+        <v>-228.13</v>
       </c>
       <c r="CC6" t="n">
-        <v>-227.67</v>
+        <v>-228.13</v>
       </c>
       <c r="CD6" t="n">
-        <v>-227.67</v>
+        <v>-228.13</v>
       </c>
       <c r="CE6" t="n">
-        <v>-227.67</v>
+        <v>-228.13</v>
       </c>
     </row>
     <row r="7">
@@ -6201,31 +6201,31 @@
         <v>-247.35</v>
       </c>
       <c r="AI7" t="n">
-        <v>-494.7</v>
+        <v>-497.67</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-742.05</v>
+        <v>-746.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>-989.4</v>
+        <v>-995.34</v>
       </c>
       <c r="AL7" t="n">
-        <v>-1236.75</v>
+        <v>-1244.17</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1484.1</v>
+        <v>-1493.01</v>
       </c>
       <c r="AN7" t="n">
-        <v>-742.05</v>
+        <v>-743.54</v>
       </c>
       <c r="AO7" t="n">
-        <v>-742.05</v>
+        <v>-743.54</v>
       </c>
       <c r="AP7" t="n">
-        <v>-742.05</v>
+        <v>-743.54</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-742.05</v>
+        <v>-743.54</v>
       </c>
       <c r="AR7" t="n">
         <v>-257.66</v>
@@ -6264,88 +6264,88 @@
         <v>-265.39</v>
       </c>
       <c r="BD7" t="n">
-        <v>-772.97</v>
+        <v>-774.52</v>
       </c>
       <c r="BE7" t="n">
-        <v>-772.97</v>
+        <v>-774.52</v>
       </c>
       <c r="BF7" t="n">
-        <v>-796.16</v>
+        <v>-797.75</v>
       </c>
       <c r="BG7" t="n">
-        <v>-796.16</v>
+        <v>-797.75</v>
       </c>
       <c r="BH7" t="n">
-        <v>-515.3099999999999</v>
+        <v>-518.41</v>
       </c>
       <c r="BI7" t="n">
-        <v>-772.97</v>
+        <v>-777.61</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-1030.63</v>
+        <v>-1036.81</v>
       </c>
       <c r="BK7" t="n">
-        <v>-1288.28</v>
+        <v>-1296.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>-1545.94</v>
+        <v>-1555.22</v>
       </c>
       <c r="BM7" t="n">
         <v>-265.39</v>
       </c>
       <c r="BN7" t="n">
-        <v>-530.77</v>
+        <v>-533.96</v>
       </c>
       <c r="BO7" t="n">
-        <v>-796.16</v>
+        <v>-800.9400000000001</v>
       </c>
       <c r="BP7" t="n">
-        <v>-1061.55</v>
+        <v>-1067.92</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-1326.93</v>
+        <v>-1334.89</v>
       </c>
       <c r="BR7" t="n">
-        <v>-1592.32</v>
+        <v>-1601.87</v>
       </c>
       <c r="BS7" t="n">
-        <v>-3184.64</v>
+        <v>-3197.38</v>
       </c>
       <c r="BT7" t="n">
-        <v>-2968.21</v>
+        <v>-2980.08</v>
       </c>
       <c r="BU7" t="n">
         <v>-278.27</v>
       </c>
       <c r="BV7" t="n">
-        <v>-3339.23</v>
+        <v>-3352.59</v>
       </c>
       <c r="BW7" t="n">
-        <v>-556.54</v>
+        <v>-559.88</v>
       </c>
       <c r="BX7" t="n">
-        <v>-834.8099999999999</v>
+        <v>-839.8200000000001</v>
       </c>
       <c r="BY7" t="n">
-        <v>-1113.08</v>
+        <v>-1119.76</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-1391.35</v>
+        <v>-1399.7</v>
       </c>
       <c r="CA7" t="n">
-        <v>-1669.62</v>
+        <v>-1679.63</v>
       </c>
       <c r="CB7" t="n">
-        <v>-834.8099999999999</v>
+        <v>-836.48</v>
       </c>
       <c r="CC7" t="n">
-        <v>-834.8099999999999</v>
+        <v>-836.48</v>
       </c>
       <c r="CD7" t="n">
-        <v>-834.8099999999999</v>
+        <v>-836.48</v>
       </c>
       <c r="CE7" t="n">
-        <v>-834.8099999999999</v>
+        <v>-836.48</v>
       </c>
     </row>
     <row r="8">
@@ -6496,31 +6496,31 @@
         <v>166.52</v>
       </c>
       <c r="AI8" t="n">
-        <v>333.04</v>
+        <v>335.04</v>
       </c>
       <c r="AJ8" t="n">
-        <v>499.56</v>
+        <v>502.56</v>
       </c>
       <c r="AK8" t="n">
-        <v>666.09</v>
+        <v>670.08</v>
       </c>
       <c r="AL8" t="n">
-        <v>832.61</v>
+        <v>837.6</v>
       </c>
       <c r="AM8" t="n">
-        <v>999.13</v>
+        <v>1005.12</v>
       </c>
       <c r="AN8" t="n">
-        <v>499.56</v>
+        <v>500.56</v>
       </c>
       <c r="AO8" t="n">
-        <v>499.56</v>
+        <v>500.56</v>
       </c>
       <c r="AP8" t="n">
-        <v>499.56</v>
+        <v>500.56</v>
       </c>
       <c r="AQ8" t="n">
-        <v>499.56</v>
+        <v>500.56</v>
       </c>
       <c r="AR8" t="n">
         <v>173.46</v>
@@ -6559,88 +6559,88 @@
         <v>178.66</v>
       </c>
       <c r="BD8" t="n">
-        <v>520.38</v>
+        <v>521.42</v>
       </c>
       <c r="BE8" t="n">
-        <v>520.38</v>
+        <v>521.42</v>
       </c>
       <c r="BF8" t="n">
-        <v>535.99</v>
+        <v>537.0599999999999</v>
       </c>
       <c r="BG8" t="n">
-        <v>535.99</v>
+        <v>537.0599999999999</v>
       </c>
       <c r="BH8" t="n">
-        <v>346.92</v>
+        <v>349</v>
       </c>
       <c r="BI8" t="n">
-        <v>520.38</v>
+        <v>523.5</v>
       </c>
       <c r="BJ8" t="n">
-        <v>693.84</v>
+        <v>698</v>
       </c>
       <c r="BK8" t="n">
-        <v>867.3</v>
+        <v>872.5</v>
       </c>
       <c r="BL8" t="n">
-        <v>1040.76</v>
+        <v>1047</v>
       </c>
       <c r="BM8" t="n">
         <v>178.66</v>
       </c>
       <c r="BN8" t="n">
-        <v>357.33</v>
+        <v>359.47</v>
       </c>
       <c r="BO8" t="n">
-        <v>535.99</v>
+        <v>539.21</v>
       </c>
       <c r="BP8" t="n">
-        <v>714.65</v>
+        <v>718.9400000000001</v>
       </c>
       <c r="BQ8" t="n">
-        <v>893.3200000000001</v>
+        <v>898.6799999999999</v>
       </c>
       <c r="BR8" t="n">
-        <v>1071.98</v>
+        <v>1078.41</v>
       </c>
       <c r="BS8" t="n">
-        <v>2143.96</v>
+        <v>2152.54</v>
       </c>
       <c r="BT8" t="n">
-        <v>1998.26</v>
+        <v>2006.25</v>
       </c>
       <c r="BU8" t="n">
         <v>187.34</v>
       </c>
       <c r="BV8" t="n">
-        <v>2248.04</v>
+        <v>2257.03</v>
       </c>
       <c r="BW8" t="n">
-        <v>374.67</v>
+        <v>376.92</v>
       </c>
       <c r="BX8" t="n">
-        <v>562.01</v>
+        <v>565.38</v>
       </c>
       <c r="BY8" t="n">
-        <v>749.35</v>
+        <v>753.84</v>
       </c>
       <c r="BZ8" t="n">
-        <v>936.6799999999999</v>
+        <v>942.3</v>
       </c>
       <c r="CA8" t="n">
-        <v>1124.02</v>
+        <v>1130.76</v>
       </c>
       <c r="CB8" t="n">
-        <v>562.01</v>
+        <v>563.13</v>
       </c>
       <c r="CC8" t="n">
-        <v>562.01</v>
+        <v>563.13</v>
       </c>
       <c r="CD8" t="n">
-        <v>562.01</v>
+        <v>563.13</v>
       </c>
       <c r="CE8" t="n">
-        <v>562.01</v>
+        <v>563.13</v>
       </c>
     </row>
     <row r="9">
@@ -6791,31 +6791,31 @@
         <v>222.14</v>
       </c>
       <c r="AI9" t="n">
-        <v>444.27</v>
+        <v>446.94</v>
       </c>
       <c r="AJ9" t="n">
-        <v>666.41</v>
+        <v>670.4</v>
       </c>
       <c r="AK9" t="n">
-        <v>888.54</v>
+        <v>893.87</v>
       </c>
       <c r="AL9" t="n">
-        <v>1110.68</v>
+        <v>1117.34</v>
       </c>
       <c r="AM9" t="n">
-        <v>1332.81</v>
+        <v>1340.81</v>
       </c>
       <c r="AN9" t="n">
-        <v>666.41</v>
+        <v>667.74</v>
       </c>
       <c r="AO9" t="n">
-        <v>666.41</v>
+        <v>667.74</v>
       </c>
       <c r="AP9" t="n">
-        <v>666.41</v>
+        <v>667.74</v>
       </c>
       <c r="AQ9" t="n">
-        <v>666.41</v>
+        <v>667.74</v>
       </c>
       <c r="AR9" t="n">
         <v>231.39</v>
@@ -6854,88 +6854,88 @@
         <v>238.33</v>
       </c>
       <c r="BD9" t="n">
-        <v>694.17</v>
+        <v>695.5599999999999</v>
       </c>
       <c r="BE9" t="n">
-        <v>694.17</v>
+        <v>695.5599999999999</v>
       </c>
       <c r="BF9" t="n">
-        <v>715</v>
+        <v>716.4299999999999</v>
       </c>
       <c r="BG9" t="n">
-        <v>715</v>
+        <v>716.4299999999999</v>
       </c>
       <c r="BH9" t="n">
-        <v>462.78</v>
+        <v>465.56</v>
       </c>
       <c r="BI9" t="n">
-        <v>694.17</v>
+        <v>698.34</v>
       </c>
       <c r="BJ9" t="n">
-        <v>925.5599999999999</v>
+        <v>931.12</v>
       </c>
       <c r="BK9" t="n">
-        <v>1156.96</v>
+        <v>1163.9</v>
       </c>
       <c r="BL9" t="n">
-        <v>1388.35</v>
+        <v>1396.68</v>
       </c>
       <c r="BM9" t="n">
         <v>238.33</v>
       </c>
       <c r="BN9" t="n">
-        <v>476.67</v>
+        <v>479.53</v>
       </c>
       <c r="BO9" t="n">
-        <v>715</v>
+        <v>719.29</v>
       </c>
       <c r="BP9" t="n">
-        <v>953.33</v>
+        <v>959.05</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1191.66</v>
+        <v>1198.81</v>
       </c>
       <c r="BR9" t="n">
-        <v>1430</v>
+        <v>1438.58</v>
       </c>
       <c r="BS9" t="n">
-        <v>2859.99</v>
+        <v>2871.43</v>
       </c>
       <c r="BT9" t="n">
-        <v>2665.63</v>
+        <v>2676.29</v>
       </c>
       <c r="BU9" t="n">
         <v>249.9</v>
       </c>
       <c r="BV9" t="n">
-        <v>2998.83</v>
+        <v>3010.82</v>
       </c>
       <c r="BW9" t="n">
-        <v>499.8</v>
+        <v>502.8</v>
       </c>
       <c r="BX9" t="n">
-        <v>749.71</v>
+        <v>754.21</v>
       </c>
       <c r="BY9" t="n">
-        <v>999.61</v>
+        <v>1005.61</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1249.51</v>
+        <v>1257.01</v>
       </c>
       <c r="CA9" t="n">
-        <v>1499.41</v>
+        <v>1508.41</v>
       </c>
       <c r="CB9" t="n">
-        <v>749.71</v>
+        <v>751.21</v>
       </c>
       <c r="CC9" t="n">
-        <v>749.71</v>
+        <v>751.21</v>
       </c>
       <c r="CD9" t="n">
-        <v>749.71</v>
+        <v>751.21</v>
       </c>
       <c r="CE9" t="n">
-        <v>749.71</v>
+        <v>751.21</v>
       </c>
     </row>
     <row r="10">
@@ -7086,31 +7086,31 @@
         <v>148.6</v>
       </c>
       <c r="AI10" t="n">
-        <v>297.2</v>
+        <v>298.98</v>
       </c>
       <c r="AJ10" t="n">
-        <v>445.8</v>
+        <v>448.47</v>
       </c>
       <c r="AK10" t="n">
-        <v>594.4</v>
+        <v>597.96</v>
       </c>
       <c r="AL10" t="n">
-        <v>743</v>
+        <v>747.46</v>
       </c>
       <c r="AM10" t="n">
-        <v>891.6</v>
+        <v>896.95</v>
       </c>
       <c r="AN10" t="n">
-        <v>445.8</v>
+        <v>446.69</v>
       </c>
       <c r="AO10" t="n">
-        <v>445.8</v>
+        <v>446.69</v>
       </c>
       <c r="AP10" t="n">
-        <v>445.8</v>
+        <v>446.69</v>
       </c>
       <c r="AQ10" t="n">
-        <v>445.8</v>
+        <v>446.69</v>
       </c>
       <c r="AR10" t="n">
         <v>154.79</v>
@@ -7149,88 +7149,88 @@
         <v>159.43</v>
       </c>
       <c r="BD10" t="n">
-        <v>464.37</v>
+        <v>465.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>464.37</v>
+        <v>465.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>478.3</v>
+        <v>479.26</v>
       </c>
       <c r="BG10" t="n">
-        <v>478.3</v>
+        <v>479.26</v>
       </c>
       <c r="BH10" t="n">
-        <v>309.58</v>
+        <v>311.44</v>
       </c>
       <c r="BI10" t="n">
-        <v>464.37</v>
+        <v>467.16</v>
       </c>
       <c r="BJ10" t="n">
-        <v>619.16</v>
+        <v>622.88</v>
       </c>
       <c r="BK10" t="n">
-        <v>773.96</v>
+        <v>778.6</v>
       </c>
       <c r="BL10" t="n">
-        <v>928.75</v>
+        <v>934.3200000000001</v>
       </c>
       <c r="BM10" t="n">
         <v>159.43</v>
       </c>
       <c r="BN10" t="n">
-        <v>318.87</v>
+        <v>320.78</v>
       </c>
       <c r="BO10" t="n">
-        <v>478.3</v>
+        <v>481.17</v>
       </c>
       <c r="BP10" t="n">
-        <v>637.74</v>
+        <v>641.5700000000001</v>
       </c>
       <c r="BQ10" t="n">
-        <v>797.17</v>
+        <v>801.96</v>
       </c>
       <c r="BR10" t="n">
-        <v>956.61</v>
+        <v>962.35</v>
       </c>
       <c r="BS10" t="n">
-        <v>1913.22</v>
+        <v>1920.87</v>
       </c>
       <c r="BT10" t="n">
-        <v>1783.19</v>
+        <v>1790.33</v>
       </c>
       <c r="BU10" t="n">
         <v>167.17</v>
       </c>
       <c r="BV10" t="n">
-        <v>2006.09</v>
+        <v>2014.12</v>
       </c>
       <c r="BW10" t="n">
-        <v>334.35</v>
+        <v>336.36</v>
       </c>
       <c r="BX10" t="n">
-        <v>501.52</v>
+        <v>504.53</v>
       </c>
       <c r="BY10" t="n">
-        <v>668.7</v>
+        <v>672.71</v>
       </c>
       <c r="BZ10" t="n">
-        <v>835.87</v>
+        <v>840.89</v>
       </c>
       <c r="CA10" t="n">
-        <v>1003.05</v>
+        <v>1009.07</v>
       </c>
       <c r="CB10" t="n">
-        <v>501.52</v>
+        <v>502.53</v>
       </c>
       <c r="CC10" t="n">
-        <v>501.52</v>
+        <v>502.53</v>
       </c>
       <c r="CD10" t="n">
-        <v>501.52</v>
+        <v>502.53</v>
       </c>
       <c r="CE10" t="n">
-        <v>501.52</v>
+        <v>502.53</v>
       </c>
     </row>
     <row r="11">
@@ -7381,31 +7381,31 @@
         <v>-160.04</v>
       </c>
       <c r="AI11" t="n">
-        <v>-320.08</v>
+        <v>-322</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-480.12</v>
+        <v>-483</v>
       </c>
       <c r="AK11" t="n">
-        <v>-640.16</v>
+        <v>-644</v>
       </c>
       <c r="AL11" t="n">
-        <v>-800.2</v>
+        <v>-805</v>
       </c>
       <c r="AM11" t="n">
-        <v>-960.24</v>
+        <v>-966.01</v>
       </c>
       <c r="AN11" t="n">
-        <v>-480.12</v>
+        <v>-481.08</v>
       </c>
       <c r="AO11" t="n">
-        <v>-480.12</v>
+        <v>-481.08</v>
       </c>
       <c r="AP11" t="n">
-        <v>-480.12</v>
+        <v>-481.08</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-480.12</v>
+        <v>-481.08</v>
       </c>
       <c r="AR11" t="n">
         <v>-166.71</v>
@@ -7444,88 +7444,88 @@
         <v>-171.71</v>
       </c>
       <c r="BD11" t="n">
-        <v>-500.13</v>
+        <v>-501.13</v>
       </c>
       <c r="BE11" t="n">
-        <v>-500.13</v>
+        <v>-501.13</v>
       </c>
       <c r="BF11" t="n">
-        <v>-515.13</v>
+        <v>-516.16</v>
       </c>
       <c r="BG11" t="n">
-        <v>-515.13</v>
+        <v>-516.16</v>
       </c>
       <c r="BH11" t="n">
-        <v>-333.42</v>
+        <v>-335.42</v>
       </c>
       <c r="BI11" t="n">
-        <v>-500.13</v>
+        <v>-503.13</v>
       </c>
       <c r="BJ11" t="n">
-        <v>-666.84</v>
+        <v>-670.84</v>
       </c>
       <c r="BK11" t="n">
-        <v>-833.55</v>
+        <v>-838.55</v>
       </c>
       <c r="BL11" t="n">
-        <v>-1000.25</v>
+        <v>-1006.26</v>
       </c>
       <c r="BM11" t="n">
         <v>-171.71</v>
       </c>
       <c r="BN11" t="n">
-        <v>-343.42</v>
+        <v>-345.48</v>
       </c>
       <c r="BO11" t="n">
-        <v>-515.13</v>
+        <v>-518.22</v>
       </c>
       <c r="BP11" t="n">
-        <v>-686.84</v>
+        <v>-690.96</v>
       </c>
       <c r="BQ11" t="n">
-        <v>-858.55</v>
+        <v>-863.7</v>
       </c>
       <c r="BR11" t="n">
-        <v>-1030.26</v>
+        <v>-1036.44</v>
       </c>
       <c r="BS11" t="n">
-        <v>-2060.52</v>
+        <v>-2068.77</v>
       </c>
       <c r="BT11" t="n">
-        <v>-1920.49</v>
+        <v>-1928.17</v>
       </c>
       <c r="BU11" t="n">
         <v>-180.05</v>
       </c>
       <c r="BV11" t="n">
-        <v>-2160.55</v>
+        <v>-2169.19</v>
       </c>
       <c r="BW11" t="n">
-        <v>-360.09</v>
+        <v>-362.25</v>
       </c>
       <c r="BX11" t="n">
-        <v>-540.14</v>
+        <v>-543.38</v>
       </c>
       <c r="BY11" t="n">
-        <v>-720.1799999999999</v>
+        <v>-724.5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-900.23</v>
+        <v>-905.63</v>
       </c>
       <c r="CA11" t="n">
-        <v>-1080.27</v>
+        <v>-1086.76</v>
       </c>
       <c r="CB11" t="n">
-        <v>-540.14</v>
+        <v>-541.22</v>
       </c>
       <c r="CC11" t="n">
-        <v>-540.14</v>
+        <v>-541.22</v>
       </c>
       <c r="CD11" t="n">
-        <v>-540.14</v>
+        <v>-541.22</v>
       </c>
       <c r="CE11" t="n">
-        <v>-540.14</v>
+        <v>-541.22</v>
       </c>
     </row>
     <row r="12">
@@ -7676,31 +7676,31 @@
         <v>-260.09</v>
       </c>
       <c r="AI12" t="n">
-        <v>-520.1799999999999</v>
+        <v>-523.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-780.27</v>
+        <v>-784.95</v>
       </c>
       <c r="AK12" t="n">
-        <v>-1040.36</v>
+        <v>-1046.61</v>
       </c>
       <c r="AL12" t="n">
-        <v>-1300.45</v>
+        <v>-1308.26</v>
       </c>
       <c r="AM12" t="n">
-        <v>-1560.55</v>
+        <v>-1569.91</v>
       </c>
       <c r="AN12" t="n">
-        <v>-780.27</v>
+        <v>-781.83</v>
       </c>
       <c r="AO12" t="n">
-        <v>-780.27</v>
+        <v>-781.83</v>
       </c>
       <c r="AP12" t="n">
-        <v>-780.27</v>
+        <v>-781.83</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-780.27</v>
+        <v>-781.83</v>
       </c>
       <c r="AR12" t="n">
         <v>-270.93</v>
@@ -7739,88 +7739,88 @@
         <v>-279.06</v>
       </c>
       <c r="BD12" t="n">
-        <v>-812.78</v>
+        <v>-814.41</v>
       </c>
       <c r="BE12" t="n">
-        <v>-812.78</v>
+        <v>-814.41</v>
       </c>
       <c r="BF12" t="n">
-        <v>-837.17</v>
+        <v>-838.84</v>
       </c>
       <c r="BG12" t="n">
-        <v>-837.17</v>
+        <v>-838.84</v>
       </c>
       <c r="BH12" t="n">
-        <v>-541.86</v>
+        <v>-545.11</v>
       </c>
       <c r="BI12" t="n">
-        <v>-812.78</v>
+        <v>-817.66</v>
       </c>
       <c r="BJ12" t="n">
-        <v>-1083.71</v>
+        <v>-1090.21</v>
       </c>
       <c r="BK12" t="n">
-        <v>-1354.64</v>
+        <v>-1362.77</v>
       </c>
       <c r="BL12" t="n">
-        <v>-1625.57</v>
+        <v>-1635.32</v>
       </c>
       <c r="BM12" t="n">
         <v>-279.06</v>
       </c>
       <c r="BN12" t="n">
-        <v>-558.11</v>
+        <v>-561.46</v>
       </c>
       <c r="BO12" t="n">
-        <v>-837.17</v>
+        <v>-842.1900000000001</v>
       </c>
       <c r="BP12" t="n">
-        <v>-1116.22</v>
+        <v>-1122.92</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-1395.28</v>
+        <v>-1403.65</v>
       </c>
       <c r="BR12" t="n">
-        <v>-1674.34</v>
+        <v>-1684.38</v>
       </c>
       <c r="BS12" t="n">
-        <v>-3348.67</v>
+        <v>-3362.06</v>
       </c>
       <c r="BT12" t="n">
-        <v>-3121.09</v>
+        <v>-3133.57</v>
       </c>
       <c r="BU12" t="n">
         <v>-292.6</v>
       </c>
       <c r="BV12" t="n">
-        <v>-3511.23</v>
+        <v>-3525.27</v>
       </c>
       <c r="BW12" t="n">
-        <v>-585.2</v>
+        <v>-588.72</v>
       </c>
       <c r="BX12" t="n">
-        <v>-877.8099999999999</v>
+        <v>-883.0700000000001</v>
       </c>
       <c r="BY12" t="n">
-        <v>-1170.41</v>
+        <v>-1177.43</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-1463.01</v>
+        <v>-1471.79</v>
       </c>
       <c r="CA12" t="n">
-        <v>-1755.61</v>
+        <v>-1766.15</v>
       </c>
       <c r="CB12" t="n">
-        <v>-877.8099999999999</v>
+        <v>-879.5599999999999</v>
       </c>
       <c r="CC12" t="n">
-        <v>-877.8099999999999</v>
+        <v>-879.5599999999999</v>
       </c>
       <c r="CD12" t="n">
-        <v>-877.8099999999999</v>
+        <v>-879.5599999999999</v>
       </c>
       <c r="CE12" t="n">
-        <v>-877.8099999999999</v>
+        <v>-879.5599999999999</v>
       </c>
     </row>
   </sheetData>
